--- a/documentation/Construccion y Evolucion/1. Solicitudes de cambio/CR 4.xlsx
+++ b/documentation/Construccion y Evolucion/1. Solicitudes de cambio/CR 4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Windows\Descargas\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\translator\TraductorBrailleEspanol\documentation\Construccion y Evolucion\1. Solicitudes de cambio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{893C892F-49DE-48B4-BD8A-A3FE3C592174}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7D1EEDF2-5925-497F-8C0F-B057D3117456}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11310" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20640" windowHeight="11160" activeTab="1" xr2:uid="{AAACD53E-982C-4521-B07F-7DC6290E23F5}"/>
   </bookViews>
   <sheets>
     <sheet name="CR Formato" sheetId="1" r:id="rId1"/>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="57">
   <si>
     <t>CHANGE REQUEST</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>Opción recomendada: Actualizar el manual existente (Alternativa 1), dado que proporciona una solución rápida y eficiente, reutilizando gran parte del contenido actual, y puede completarse en un tiempo razonable sin afectar significativamente otros proyectos o cronogramas.</t>
+  </si>
+  <si>
+    <t>Bajo</t>
   </si>
 </sst>
 </file>
@@ -520,6 +523,16 @@
     </xf>
     <xf numFmtId="14" fontId="0" fillId="3" borderId="16" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="16" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -547,42 +560,32 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -990,12 +993,12 @@
       <c r="C7" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="25" t="s">
+      <c r="D7" s="29" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="25"/>
-      <c r="F7" s="25"/>
-      <c r="G7" s="25"/>
+      <c r="E7" s="29"/>
+      <c r="F7" s="29"/>
+      <c r="G7" s="29"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
@@ -1011,12 +1014,12 @@
       <c r="C10" t="s">
         <v>4</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="29" t="s">
         <v>39</v>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
+      <c r="E10" s="29"/>
+      <c r="F10" s="29"/>
+      <c r="G10" s="29"/>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="2:8" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
@@ -1028,12 +1031,12 @@
       <c r="C12" t="s">
         <v>5</v>
       </c>
-      <c r="D12" s="25" t="s">
+      <c r="D12" s="29" t="s">
         <v>37</v>
       </c>
-      <c r="E12" s="25"/>
-      <c r="F12" s="25"/>
-      <c r="G12" s="25"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
@@ -1049,22 +1052,22 @@
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B15" s="4"/>
-      <c r="C15" s="26" t="s">
+      <c r="C15" s="30" t="s">
         <v>40</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="27"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
+      <c r="D15" s="31"/>
+      <c r="E15" s="31"/>
+      <c r="F15" s="31"/>
+      <c r="G15" s="32"/>
       <c r="H15" s="7"/>
     </row>
     <row r="16" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B16" s="4"/>
-      <c r="C16" s="29"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="30"/>
-      <c r="G16" s="31"/>
+      <c r="C16" s="33"/>
+      <c r="D16" s="34"/>
+      <c r="E16" s="34"/>
+      <c r="F16" s="34"/>
+      <c r="G16" s="35"/>
       <c r="H16" s="7"/>
     </row>
     <row r="17" spans="2:8" x14ac:dyDescent="0.25">
@@ -1073,10 +1076,10 @@
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B18" s="4"/>
-      <c r="C18" s="32" t="s">
+      <c r="C18" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="33"/>
+      <c r="D18" s="37"/>
       <c r="E18" s="8" t="s">
         <v>8</v>
       </c>
@@ -1246,11 +1249,11 @@
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B32" s="4"/>
-      <c r="C32" s="34"/>
-      <c r="D32" s="35"/>
-      <c r="E32" s="35"/>
-      <c r="F32" s="35"/>
-      <c r="G32" s="36"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="27"/>
+      <c r="E32" s="27"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="28"/>
       <c r="H32" s="7"/>
     </row>
     <row r="33" spans="2:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -1325,7 +1328,7 @@
       <c r="F5" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="39">
+      <c r="G5" s="25">
         <v>45516</v>
       </c>
       <c r="H5" s="7"/>
@@ -1339,12 +1342,12 @@
       <c r="C7" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="D7" s="38" t="s">
         <v>45</v>
       </c>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
+      <c r="E7" s="38"/>
+      <c r="F7" s="38"/>
+      <c r="G7" s="38"/>
       <c r="H7" s="7"/>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
@@ -1364,49 +1367,49 @@
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" s="4"/>
-      <c r="C10" s="40" t="s">
+      <c r="C10" s="39" t="s">
         <v>46</v>
       </c>
-      <c r="D10" s="41"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
+      <c r="D10" s="40"/>
+      <c r="E10" s="40"/>
+      <c r="F10" s="40"/>
+      <c r="G10" s="41"/>
       <c r="H10" s="7"/>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" s="4"/>
-      <c r="C11" s="43"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="42"/>
+      <c r="C11" s="42"/>
+      <c r="D11" s="40"/>
+      <c r="E11" s="40"/>
+      <c r="F11" s="40"/>
+      <c r="G11" s="41"/>
       <c r="H11" s="7"/>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" s="4"/>
-      <c r="C12" s="43"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="42"/>
+      <c r="C12" s="42"/>
+      <c r="D12" s="40"/>
+      <c r="E12" s="40"/>
+      <c r="F12" s="40"/>
+      <c r="G12" s="41"/>
       <c r="H12" s="7"/>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" s="4"/>
-      <c r="C13" s="43"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="41"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="42"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="40"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="41"/>
       <c r="H13" s="7"/>
     </row>
     <row r="14" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B14" s="4"/>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="45"/>
-      <c r="F14" s="45"/>
-      <c r="G14" s="46"/>
+      <c r="C14" s="43"/>
+      <c r="D14" s="44"/>
+      <c r="E14" s="44"/>
+      <c r="F14" s="44"/>
+      <c r="G14" s="45"/>
       <c r="H14" s="7"/>
     </row>
     <row r="15" spans="2:8" x14ac:dyDescent="0.25">
@@ -1425,12 +1428,12 @@
       <c r="C17" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="34" t="s">
+      <c r="D17" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="E17" s="35"/>
-      <c r="F17" s="35"/>
-      <c r="G17" s="36"/>
+      <c r="E17" s="27"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="28"/>
       <c r="H17" s="7"/>
     </row>
     <row r="18" spans="2:8" x14ac:dyDescent="0.25">
@@ -1438,12 +1441,12 @@
       <c r="C18" s="8" t="s">
         <v>47</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="36" t="s">
         <v>48</v>
       </c>
       <c r="E18" s="52"/>
       <c r="F18" s="52"/>
-      <c r="G18" s="33"/>
+      <c r="G18" s="37"/>
       <c r="H18" s="7"/>
     </row>
     <row r="19" spans="2:8" x14ac:dyDescent="0.25">
@@ -1451,12 +1454,12 @@
       <c r="C19" s="8" t="s">
         <v>49</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="36" t="s">
         <v>50</v>
       </c>
       <c r="E19" s="52"/>
       <c r="F19" s="52"/>
-      <c r="G19" s="33"/>
+      <c r="G19" s="37"/>
       <c r="H19" s="7"/>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.25">
@@ -1464,27 +1467,27 @@
       <c r="C20" s="8" t="s">
         <v>51</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="36" t="s">
         <v>52</v>
       </c>
       <c r="E20" s="52"/>
       <c r="F20" s="52"/>
-      <c r="G20" s="33"/>
+      <c r="G20" s="37"/>
       <c r="H20" s="7"/>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B21" s="4"/>
       <c r="C21" s="8"/>
-      <c r="D21" s="34"/>
-      <c r="E21" s="35"/>
-      <c r="F21" s="35"/>
-      <c r="G21" s="36"/>
+      <c r="D21" s="26"/>
+      <c r="E21" s="27"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="28"/>
       <c r="H21" s="7"/>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B22" s="4"/>
-      <c r="F22" s="38"/>
-      <c r="G22" s="38"/>
+      <c r="F22" s="46"/>
+      <c r="G22" s="46"/>
       <c r="H22" s="7"/>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.25">
@@ -1505,6 +1508,9 @@
       <c r="B25" s="4"/>
       <c r="C25" t="s">
         <v>33</v>
+      </c>
+      <c r="D25" t="s">
+        <v>56</v>
       </c>
       <c r="H25" s="7"/>
     </row>
@@ -1574,9 +1580,9 @@
     <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="4"/>
       <c r="C33" s="50"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="37"/>
-      <c r="F33" s="37"/>
+      <c r="D33" s="38"/>
+      <c r="E33" s="38"/>
+      <c r="F33" s="38"/>
       <c r="G33" s="51"/>
       <c r="H33" s="7"/>
     </row>
@@ -1606,23 +1612,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100B08EDF72D49EA44AB90F024D99D2B5E3" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="d6207507167e209dbfd27b884ee120ca">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96" xmlns:ns4="56eae398-d265-4f71-b30c-62c529056c9f" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7ebf290c66ec3e245dfaec660d84bc70" ns3:_="" ns4:_="">
     <xsd:import namespace="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96"/>
@@ -1869,10 +1858,38 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BE880B-0D64-411C-BD75-74863A321A9B}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A299727D-0257-4624-9B82-EEF7D307A1F7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96"/>
+    <ds:schemaRef ds:uri="56eae398-d265-4f71-b30c-62c529056c9f"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -1895,20 +1912,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A299727D-0257-4624-9B82-EEF7D307A1F7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{B3BE880B-0D64-411C-BD75-74863A321A9B}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="f7b1a7ea-1dd0-43bd-8f52-dd9459d0ec96"/>
-    <ds:schemaRef ds:uri="56eae398-d265-4f71-b30c-62c529056c9f"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>